--- a/results/DR_results/02_taxa_assemblage/Wards_LDA/cluster_classifier/tables/lda_axes_summary.xlsx
+++ b/results/DR_results/02_taxa_assemblage/Wards_LDA/cluster_classifier/tables/lda_axes_summary.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>80.36</v>
+        <v>73.02</v>
       </c>
       <c r="C2" t="n">
-        <v>80.36</v>
+        <v>73.02</v>
       </c>
     </row>
     <row r="3">
@@ -465,7 +465,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19.64</v>
+        <v>26.98</v>
       </c>
       <c r="C3" t="n">
         <v>100</v>
